--- a/docs/herramientas-mx/diseno_carrito.xlsx
+++ b/docs/herramientas-mx/diseno_carrito.xlsx
@@ -7,13 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Acomodo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Estrategias" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Verificacion" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sueltos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Parametros" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cambios_sesion_nocturna" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Comparacion_bases" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Acomodo_3D_vigente" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Acomodo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Estrategias" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Verificacion" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sueltos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Parametros" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cambios_sesion_nocturna" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Comparacion_bases" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +54,11 @@
         <fgColor rgb="001B5E20"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3A5F"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -66,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -74,6 +80,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,6 +446,6197 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:R88"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>modulo</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>caja</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>cajon</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>pieza</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>girada</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>estado 3D</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>holgura minima mm</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>chequeo que la fija</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>rebaje de dedo</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Posiciones vigentes tras el chequeo 3D de la sesion nocturna 2 (#338): scripts/interferencias_3d.py. Las otras hojas son las de la sesion 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C1-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>IMP38</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Llave de impacto M18 FUEL 3/8 2854-20 (sin bateria)</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>122</v>
+      </c>
+      <c r="K2" t="n">
+        <v>202</v>
+      </c>
+      <c r="L2" t="n">
+        <v>65</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C1-02</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ROTO18</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rotomartillo M18 1/2 3602-20 (sin bateria)</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>140</v>
+      </c>
+      <c r="H3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>202</v>
+      </c>
+      <c r="K3" t="n">
+        <v>147</v>
+      </c>
+      <c r="L3" t="n">
+        <v>56</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C1-03</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TORPEDO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nivel torpedo magnetico 9 in Husky</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>354</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>45</v>
+      </c>
+      <c r="K4" t="n">
+        <v>230</v>
+      </c>
+      <c r="L4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C1-04</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BAT1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bateria M18 CP2.0</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>220</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>118</v>
+      </c>
+      <c r="K5" t="n">
+        <v>79</v>
+      </c>
+      <c r="L5" t="n">
+        <v>55</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C1-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BAT2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bateria M18 CP2.0</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>136</v>
+      </c>
+      <c r="H6" t="n">
+        <v>220</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>118</v>
+      </c>
+      <c r="K6" t="n">
+        <v>79</v>
+      </c>
+      <c r="L6" t="n">
+        <v>55</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PASA</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>a herramienta vs fichas ajenas</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C1-06</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MINIP</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mini pinza de corte al ras 48-22-6105</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>266</v>
+      </c>
+      <c r="H7" t="n">
+        <v>248</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>127</v>
+      </c>
+      <c r="K7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L7" t="n">
+        <v>13</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>solo lado 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C2-01</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>IMP14</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Atornillador de impacto M18 3650-20 (sin bateria)</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>112</v>
+      </c>
+      <c r="K8" t="n">
+        <v>196</v>
+      </c>
+      <c r="L8" t="n">
+        <v>53</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>solo lado 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C2-02</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WIHA-PC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pinza de corte diagonal aislada 160 (32933)</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>130</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>55</v>
+      </c>
+      <c r="K9" t="n">
+        <v>160</v>
+      </c>
+      <c r="L9" t="n">
+        <v>20</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C2-03</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AJ12</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Llave ajustable 12 in Husky 17018</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>221</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>78</v>
+      </c>
+      <c r="K10" t="n">
+        <v>305</v>
+      </c>
+      <c r="L10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>d dedos lado 2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C2-04</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NAVAJA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Navaja retractil Anvil</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>311</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>88</v>
+      </c>
+      <c r="K11" t="n">
+        <v>224</v>
+      </c>
+      <c r="L11" t="n">
+        <v>20</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C2-05</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>WIHA-PE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pinza combinada aislada 200 (32930)</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>214</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>203</v>
+      </c>
+      <c r="K12" t="n">
+        <v>60</v>
+      </c>
+      <c r="L12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>VERN</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vernier digital 6 in Truper CALDI-6MP</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>237</v>
+      </c>
+      <c r="K13" t="n">
+        <v>80</v>
+      </c>
+      <c r="L13" t="n">
+        <v>20</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>d dedos lado 2</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BROCAS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Juego 15 brocas HSS 1/16-1/2 Truper (estuche)</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>255</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>150</v>
+      </c>
+      <c r="K14" t="n">
+        <v>80</v>
+      </c>
+      <c r="L14" t="n">
+        <v>20</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-03</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PDIAG</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pinza diagonal 7 in Husky 903465</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>223</v>
+      </c>
+      <c r="H15" t="n">
+        <v>166</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>178</v>
+      </c>
+      <c r="K15" t="n">
+        <v>58</v>
+      </c>
+      <c r="L15" t="n">
+        <v>17</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>PASA</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>a herramienta vs fichas ajenas</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-04</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AJ8</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Llave ajustable 8 in Husky 17016</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>166</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>205</v>
+      </c>
+      <c r="K16" t="n">
+        <v>56</v>
+      </c>
+      <c r="L16" t="n">
+        <v>15</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-05</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CHOF8</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pinza de chofer 8 in Truper 17301</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>234</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>203</v>
+      </c>
+      <c r="K17" t="n">
+        <v>50</v>
+      </c>
+      <c r="L17" t="n">
+        <v>15</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-06</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PELEC</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pinza de electricista 9 in Husky 709195</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>104</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>250</v>
+      </c>
+      <c r="K18" t="n">
+        <v>50</v>
+      </c>
+      <c r="L18" t="n">
+        <v>15</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-01</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MATR</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Matraca 3/8 + dados (juego Husky P, 3/8)</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>200</v>
+      </c>
+      <c r="K19" t="n">
+        <v>280</v>
+      </c>
+      <c r="L19" t="n">
+        <v>45</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>solo lado 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>COMB7</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Juego 7 llaves combinadas matraca Husky (en su riel)</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>175</v>
+      </c>
+      <c r="K20" t="n">
+        <v>245</v>
+      </c>
+      <c r="L20" t="n">
+        <v>45</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-03</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>WIHA-DS1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Desarmador aislado PH1 x 80 (32101)</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>218</v>
+      </c>
+      <c r="H21" t="n">
+        <v>263</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>190</v>
+      </c>
+      <c r="K21" t="n">
+        <v>30</v>
+      </c>
+      <c r="L21" t="n">
+        <v>30</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C5-01</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>TAZON</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tazon magnetico Husky</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>248</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>150</v>
+      </c>
+      <c r="K22" t="n">
+        <v>150</v>
+      </c>
+      <c r="L22" t="n">
+        <v>40</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C5-02</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>HDS-A</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>3 desarmadores Husky (P1, P1, P2)</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>230</v>
+      </c>
+      <c r="K23" t="n">
+        <v>100</v>
+      </c>
+      <c r="L23" t="n">
+        <v>32</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>d dedos lado 2</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C5-03</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>WIHA-DS2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Desarmador aislado PH2 x 100 (32102)</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>124</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>215</v>
+      </c>
+      <c r="K24" t="n">
+        <v>32</v>
+      </c>
+      <c r="L24" t="n">
+        <v>32</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C5-04</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PRES6C</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pinza de presion C 6 in Torque Lock 48-22-3532</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>168</v>
+      </c>
+      <c r="H25" t="n">
+        <v>174</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>152</v>
+      </c>
+      <c r="K25" t="n">
+        <v>70</v>
+      </c>
+      <c r="L25" t="n">
+        <v>22</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C5-05</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>FLEX1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Flexometro 5 m Stanley 30-615</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>332</v>
+      </c>
+      <c r="H26" t="n">
+        <v>174</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>70</v>
+      </c>
+      <c r="K26" t="n">
+        <v>60</v>
+      </c>
+      <c r="L26" t="n">
+        <v>40</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C5-06</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ESCAL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Juego 3 brocas escalonadas Truper</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>174</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>150</v>
+      </c>
+      <c r="K27" t="n">
+        <v>90</v>
+      </c>
+      <c r="L27" t="n">
+        <v>35</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C5-07</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>FLEX2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Flexometro 5 m Stanley 30-615</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>332</v>
+      </c>
+      <c r="H28" t="n">
+        <v>246</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>70</v>
+      </c>
+      <c r="K28" t="n">
+        <v>60</v>
+      </c>
+      <c r="L28" t="n">
+        <v>40</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>d dedos lado 2</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C5-08</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>WIHA-DS4</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Desarmador aislado plano 4.5 x 100 (32023)</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>276</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>215</v>
+      </c>
+      <c r="K29" t="n">
+        <v>30</v>
+      </c>
+      <c r="L29" t="n">
+        <v>30</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-01</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HDS-B</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>3 desarmadores Husky (P2 x3)</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>100</v>
+      </c>
+      <c r="K30" t="n">
+        <v>230</v>
+      </c>
+      <c r="L30" t="n">
+        <v>32</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>solo lado 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-02</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PRES11</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Pinza de presion C 11 in Torque Lock 48-22-3531</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>118</v>
+      </c>
+      <c r="H31" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>279</v>
+      </c>
+      <c r="K31" t="n">
+        <v>110</v>
+      </c>
+      <c r="L31" t="n">
+        <v>25</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>d dedos lado 2</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>solo lado 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-03</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>EXTS</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Extensiones 3/8 (6 in, 10 in, oscilantes) y palanca</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>118</v>
+      </c>
+      <c r="H32" t="n">
+        <v>128</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>260</v>
+      </c>
+      <c r="K32" t="n">
+        <v>80</v>
+      </c>
+      <c r="L32" t="n">
+        <v>25</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-04</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PREC6</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Juego 6 desarmadores de precision 48-22-2606 (estuche)</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>118</v>
+      </c>
+      <c r="H33" t="n">
+        <v>220</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>190</v>
+      </c>
+      <c r="K33" t="n">
+        <v>90</v>
+      </c>
+      <c r="L33" t="n">
+        <v>25</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>solo lado 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-05</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ADAP</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Juego 3 adaptadores 1/4-3/8-1/2</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>320</v>
+      </c>
+      <c r="H34" t="n">
+        <v>220</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>70</v>
+      </c>
+      <c r="K34" t="n">
+        <v>40</v>
+      </c>
+      <c r="L34" t="n">
+        <v>25</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C7-01</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>MART</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Martillo una curva 16 oz Truper MA-16F</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>6</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>340</v>
+      </c>
+      <c r="K35" t="n">
+        <v>130</v>
+      </c>
+      <c r="L35" t="n">
+        <v>30</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>d dedos lado 2</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>solo lado 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C7-02</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>WIHA-DS3</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Desarmador aislado plano 3.0 x 100 (32012)</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>358</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>28</v>
+      </c>
+      <c r="K36" t="n">
+        <v>205</v>
+      </c>
+      <c r="L36" t="n">
+        <v>28</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C7-03</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PRES7</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pinza de presion 7 in mordaza recta Husky</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>148</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>182</v>
+      </c>
+      <c r="K37" t="n">
+        <v>62</v>
+      </c>
+      <c r="L37" t="n">
+        <v>23</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C7-04</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WIHA-PP</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pinza de punta aislada 160 (32926)</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>272</v>
+      </c>
+      <c r="H38" t="n">
+        <v>148</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>55</v>
+      </c>
+      <c r="K38" t="n">
+        <v>160</v>
+      </c>
+      <c r="L38" t="n">
+        <v>20</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C7-05</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PRES10</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Pinza de presion 10 in mordaza curva Husky 709204</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>223</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>254</v>
+      </c>
+      <c r="K39" t="n">
+        <v>66</v>
+      </c>
+      <c r="L39" t="n">
+        <v>26</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>2</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>48-22-8420</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C8-01</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ESM45</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mini esmeriladora 4-1/2 alambrica 6130-33 + cable</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>6</v>
+      </c>
+      <c r="H40" t="n">
+        <v>12</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>357</v>
+      </c>
+      <c r="K40" t="n">
+        <v>152</v>
+      </c>
+      <c r="L40" t="n">
+        <v>90</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>48-22-8420</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C9-01</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>CARG1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Cargador sencillo M18/M12 48-59-1812 (compra)</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" t="n">
+        <v>12</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>202</v>
+      </c>
+      <c r="K41" t="n">
+        <v>155</v>
+      </c>
+      <c r="L41" t="n">
+        <v>87</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>FTS-ELE-01-C1-01</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>EXTECH</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Amperimetro Extech MA440</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>6</v>
+      </c>
+      <c r="H42" t="n">
+        <v>6</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>70</v>
+      </c>
+      <c r="K42" t="n">
+        <v>200</v>
+      </c>
+      <c r="L42" t="n">
+        <v>40</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>2</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>solo lado 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>FTS-ELE-01-C1-02</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DETV</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Detector de voltaje Milwaukee</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>88</v>
+      </c>
+      <c r="H43" t="n">
+        <v>6</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>25</v>
+      </c>
+      <c r="K43" t="n">
+        <v>155</v>
+      </c>
+      <c r="L43" t="n">
+        <v>25</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>FTS-ELE-01-C1-03</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>FLUKE</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Pinza amperimetrica Fluke 302+</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>148</v>
+      </c>
+      <c r="H44" t="n">
+        <v>6</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>207</v>
+      </c>
+      <c r="K44" t="n">
+        <v>75</v>
+      </c>
+      <c r="L44" t="n">
+        <v>34</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>d dedos lado 2</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>solo lado 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>FTS-ELE-01-C1-04</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>HDS-C</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3 desarmadores Husky 1/4</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>148</v>
+      </c>
+      <c r="H45" t="n">
+        <v>93</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>250</v>
+      </c>
+      <c r="K45" t="n">
+        <v>100</v>
+      </c>
+      <c r="L45" t="n">
+        <v>32</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>FTS-ELE-01-C1-05</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>HDS-D</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3 desarmadores Husky 1/4, 3/16</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>148</v>
+      </c>
+      <c r="H46" t="n">
+        <v>205</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>250</v>
+      </c>
+      <c r="K46" t="n">
+        <v>100</v>
+      </c>
+      <c r="L46" t="n">
+        <v>32</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>FTS-ELE-01-C1-06</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SACAB</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>3 sacabocados Dogo 7, 13 y 19 mm</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>6</v>
+      </c>
+      <c r="H47" t="n">
+        <v>216.5</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>130</v>
+      </c>
+      <c r="K47" t="n">
+        <v>90</v>
+      </c>
+      <c r="L47" t="n">
+        <v>40</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>d dedos lado 2</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>FTS-ELE-01-C2-01</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>CRIMP</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Pinza crimpadora Weidmuller 1445070000</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H48" t="n">
+        <v>12</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>230</v>
+      </c>
+      <c r="K48" t="n">
+        <v>90</v>
+      </c>
+      <c r="L48" t="n">
+        <v>30</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>d dedos lado 2</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>FTS-ELE-01-C2-02</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PONCH</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Pinza ponchadora RJ45</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>6</v>
+      </c>
+      <c r="H49" t="n">
+        <v>114</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>200</v>
+      </c>
+      <c r="K49" t="n">
+        <v>70</v>
+      </c>
+      <c r="L49" t="n">
+        <v>25</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>FTS-ELE-01-C2-03</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PELA</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Pelacables Commercial Electric CE100821</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>218</v>
+      </c>
+      <c r="H50" t="n">
+        <v>114</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>170</v>
+      </c>
+      <c r="K50" t="n">
+        <v>55</v>
+      </c>
+      <c r="L50" t="n">
+        <v>15</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>PASA</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>8</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>a herramienta vs fichas ajenas</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ELE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>FTS-ELE-01-C2-04</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>MAPPER</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Probador de cableado Fluke MicroMapper MT-8200-49A</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>248</v>
+      </c>
+      <c r="H51" t="n">
+        <v>12</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>125</v>
+      </c>
+      <c r="K51" t="n">
+        <v>52</v>
+      </c>
+      <c r="L51" t="n">
+        <v>30</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C1-01</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>EXTQ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Extractor de quijadas 6 t Urrea 4216</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>12</v>
+      </c>
+      <c r="H52" t="n">
+        <v>6</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>160</v>
+      </c>
+      <c r="K52" t="n">
+        <v>300</v>
+      </c>
+      <c r="L52" t="n">
+        <v>50</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C1-02</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PRES10B</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Pinza de presion 10 in curva (2a)</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>306</v>
+      </c>
+      <c r="H53" t="n">
+        <v>6</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>66</v>
+      </c>
+      <c r="K53" t="n">
+        <v>254</v>
+      </c>
+      <c r="L53" t="n">
+        <v>26</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C1-03</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PRES11B</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Pinza de presion C 11 in (2a)</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>184</v>
+      </c>
+      <c r="H54" t="n">
+        <v>6</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>110</v>
+      </c>
+      <c r="K54" t="n">
+        <v>279</v>
+      </c>
+      <c r="L54" t="n">
+        <v>25</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C1-04</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>FRESA</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Fresa de carburo SF-5</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>384</v>
+      </c>
+      <c r="H55" t="n">
+        <v>6</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>15</v>
+      </c>
+      <c r="K55" t="n">
+        <v>70</v>
+      </c>
+      <c r="L55" t="n">
+        <v>15</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C2-01</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>MACH</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Juego 40 machuelos y tarrajas Truper 11442 (2 estuches)</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>330</v>
+      </c>
+      <c r="K56" t="n">
+        <v>290</v>
+      </c>
+      <c r="L56" t="n">
+        <v>45</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C2-02</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>TORX</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Juego llaves Torx/hex tipo navaja Husky</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>348</v>
+      </c>
+      <c r="H57" t="n">
+        <v>6</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>45</v>
+      </c>
+      <c r="K57" t="n">
+        <v>130</v>
+      </c>
+      <c r="L57" t="n">
+        <v>30</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C2-03</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>EXTOR</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Juego 5 extractores de tornillos Truper EXT-5</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>348</v>
+      </c>
+      <c r="H58" t="n">
+        <v>148</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>60</v>
+      </c>
+      <c r="K58" t="n">
+        <v>130</v>
+      </c>
+      <c r="L58" t="n">
+        <v>20</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>solo lado 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C3-01</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ESM45B</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mini esmeriladora 4-1/2 6130-33 (2a)</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>6</v>
+      </c>
+      <c r="H59" t="n">
+        <v>12</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>357</v>
+      </c>
+      <c r="K59" t="n">
+        <v>152</v>
+      </c>
+      <c r="L59" t="n">
+        <v>90</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C3-02</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ESCMAG</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>4 escuadras magneticas 4 in Truper (apiladas)</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>6</v>
+      </c>
+      <c r="H60" t="n">
+        <v>176</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>150</v>
+      </c>
+      <c r="K60" t="n">
+        <v>110</v>
+      </c>
+      <c r="L60" t="n">
+        <v>60</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>2</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C4-01</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>COMB10</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Juego 10 llaves combinadas Husky BITE</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>6</v>
+      </c>
+      <c r="H61" t="n">
+        <v>12</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>300</v>
+      </c>
+      <c r="K61" t="n">
+        <v>180</v>
+      </c>
+      <c r="L61" t="n">
+        <v>25</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>d dedos lado 2</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C4-02</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PRES7B</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Pinza de presion 7 in (2a, hoy faltante)</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>6</v>
+      </c>
+      <c r="H62" t="n">
+        <v>204</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>182</v>
+      </c>
+      <c r="K62" t="n">
+        <v>62</v>
+      </c>
+      <c r="L62" t="n">
+        <v>23</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C4-03</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PRES6CB</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Pinza de presion C 6 in (2a)</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>200</v>
+      </c>
+      <c r="H63" t="n">
+        <v>204</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>152</v>
+      </c>
+      <c r="K63" t="n">
+        <v>70</v>
+      </c>
+      <c r="L63" t="n">
+        <v>22</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C5-01</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>LIMAS</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>3 limas 6 in (redonda, media cana, triangular)</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>6</v>
+      </c>
+      <c r="H64" t="n">
+        <v>12</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>250</v>
+      </c>
+      <c r="K64" t="n">
+        <v>60</v>
+      </c>
+      <c r="L64" t="n">
+        <v>15</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C6-01</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>MOTO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Moto tool Truper (estuche)</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>6</v>
+      </c>
+      <c r="H65" t="n">
+        <v>12</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>300</v>
+      </c>
+      <c r="K65" t="n">
+        <v>200</v>
+      </c>
+      <c r="L65" t="n">
+        <v>80</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>48-22-8447</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>FTS-SOL-01-C6-02</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RECT</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Rectificador DeWalt DWE4887</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>6</v>
+      </c>
+      <c r="H66" t="n">
+        <v>224</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>290</v>
+      </c>
+      <c r="K66" t="n">
+        <v>70</v>
+      </c>
+      <c r="L66" t="n">
+        <v>70</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>2</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>48-22-8442</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>FTS-CIV-01-C1-01</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>TAL12</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Taladro percutor alambrico 1/2 5375-20</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>6</v>
+      </c>
+      <c r="H67" t="n">
+        <v>12</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>340</v>
+      </c>
+      <c r="K67" t="n">
+        <v>265</v>
+      </c>
+      <c r="L67" t="n">
+        <v>86</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>48-22-8442</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>FTS-CIV-01-C2-01</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SDS</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Rotomartillo SDS-Plus 5485-21 (sin estuche)</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>6</v>
+      </c>
+      <c r="H68" t="n">
+        <v>12</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>335</v>
+      </c>
+      <c r="K68" t="n">
+        <v>195</v>
+      </c>
+      <c r="L68" t="n">
+        <v>75</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>48-22-8442</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>FTS-CIV-01-C2-02</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>MANGOS</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2 mangos laterales</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>6</v>
+      </c>
+      <c r="H69" t="n">
+        <v>219</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>200</v>
+      </c>
+      <c r="K69" t="n">
+        <v>60</v>
+      </c>
+      <c r="L69" t="n">
+        <v>50</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>FTS-CIV-01-C3-01</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>SDSBIT</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Juego 15 brocas y cinceles SDS-Plus DeWalt DWA0870</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>6</v>
+      </c>
+      <c r="H70" t="n">
+        <v>12</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>400</v>
+      </c>
+      <c r="K70" t="n">
+        <v>250</v>
+      </c>
+      <c r="L70" t="n">
+        <v>45</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>FTS-CIV-01-C4-01</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>MART2</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Martillo una curva 16 oz (2o)</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>6</v>
+      </c>
+      <c r="H71" t="n">
+        <v>12</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>340</v>
+      </c>
+      <c r="K71" t="n">
+        <v>130</v>
+      </c>
+      <c r="L71" t="n">
+        <v>30</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>d dedos lado 2</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>48-22-8444</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>FTS-CIV-01-C4-02</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>CINC</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2 cinceles de corte frio 5/16x6 y 7/8x10</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>6</v>
+      </c>
+      <c r="H72" t="n">
+        <v>154</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>254</v>
+      </c>
+      <c r="K72" t="n">
+        <v>60</v>
+      </c>
+      <c r="L72" t="n">
+        <v>25</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>48-22-8420</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>FTS-CIV-01-C7-01</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>LIJA</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Lijadora orbital M18 2648-20</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>260</v>
+      </c>
+      <c r="H73" t="n">
+        <v>6</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>146</v>
+      </c>
+      <c r="K73" t="n">
+        <v>267</v>
+      </c>
+      <c r="L73" t="n">
+        <v>125</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>2</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>48-22-8420</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>FTS-CIV-01-C7-02</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>CALAD</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Sierra caladora Ryobi JS481LG</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>12</v>
+      </c>
+      <c r="H74" t="n">
+        <v>6</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>236</v>
+      </c>
+      <c r="K74" t="n">
+        <v>279</v>
+      </c>
+      <c r="L74" t="n">
+        <v>72</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>48-22-8420</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>FTS-CIV-01-C8-01</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>MAZO</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mazo de hule 16 oz Truper MH-16</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>6</v>
+      </c>
+      <c r="H75" t="n">
+        <v>12</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>357</v>
+      </c>
+      <c r="K75" t="n">
+        <v>104</v>
+      </c>
+      <c r="L75" t="n">
+        <v>51</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>48-22-8442</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>FTS-MED-01-C1-01</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>LASER</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Nivel laser verde Bosch GLL 12-22 G</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>157</v>
+      </c>
+      <c r="H76" t="n">
+        <v>198</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>64</v>
+      </c>
+      <c r="K76" t="n">
+        <v>100</v>
+      </c>
+      <c r="L76" t="n">
+        <v>104</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>PASA</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>5</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>d dedos lado 2</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>48-22-8442</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>FTS-MED-01-C1-02</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AMARRE</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>4 amarres tipo matraca 3.6 m (enrollados)</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>157</v>
+      </c>
+      <c r="H77" t="n">
+        <v>6</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>120</v>
+      </c>
+      <c r="K77" t="n">
+        <v>180</v>
+      </c>
+      <c r="L77" t="n">
+        <v>60</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>2</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>48-22-8442</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>FTS-MED-01-C1-03</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ESCCOMB</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Escuadra combinada 12 in Empire 220IM</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>12</v>
+      </c>
+      <c r="H78" t="n">
+        <v>6</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>133</v>
+      </c>
+      <c r="K78" t="n">
+        <v>304</v>
+      </c>
+      <c r="L78" t="n">
+        <v>30</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>d dedos lado 2</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>48-22-8442</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>FTS-MED-01-C1-04</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>LASER2</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Nivel laser verde Bosch (2o)</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>233</v>
+      </c>
+      <c r="H79" t="n">
+        <v>198</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>64</v>
+      </c>
+      <c r="K79" t="n">
+        <v>100</v>
+      </c>
+      <c r="L79" t="n">
+        <v>104</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>PASA</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>5</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>48-22-8442</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>FTS-MED-01-C1-05</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>GRILL</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>3 grilletes 5/8 Crosby</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>289</v>
+      </c>
+      <c r="H80" t="n">
+        <v>6</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>90</v>
+      </c>
+      <c r="K80" t="n">
+        <v>130</v>
+      </c>
+      <c r="L80" t="n">
+        <v>45</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>2</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>48-22-8442</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>FTS-MED-01-C2-01</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>TORPEDO2</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Nivel torpedo magnetico 9 in (2o)</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>6</v>
+      </c>
+      <c r="H81" t="n">
+        <v>190</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>230</v>
+      </c>
+      <c r="K81" t="n">
+        <v>45</v>
+      </c>
+      <c r="L81" t="n">
+        <v>16</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>48-22-8442</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>FTS-MED-01-C2-02</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ESCCAR</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Escuadra de carpintero 12 in Truper EC-12</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>6</v>
+      </c>
+      <c r="H82" t="n">
+        <v>12</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>304</v>
+      </c>
+      <c r="K82" t="n">
+        <v>166</v>
+      </c>
+      <c r="L82" t="n">
+        <v>14</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>d dedos lado 2</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TUB</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>FTS-TUB-01-C1-01</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>CAB34</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Cabezal 12R 3/4 NPT de repuesto</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>6</v>
+      </c>
+      <c r="H83" t="n">
+        <v>199</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>100</v>
+      </c>
+      <c r="K83" t="n">
+        <v>100</v>
+      </c>
+      <c r="L83" t="n">
+        <v>60</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>b ficha vs cajon</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TUB</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>FTS-TUB-01-C1-02</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>NIVTUB1</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Nivel para tuberia 6.5 in Milwaukee 48-22-5110</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>118</v>
+      </c>
+      <c r="H84" t="n">
+        <v>199</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>159</v>
+      </c>
+      <c r="K84" t="n">
+        <v>51</v>
+      </c>
+      <c r="L84" t="n">
+        <v>19</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TUB</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>FTS-TUB-01-C1-03</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>CAIMAN</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Llave de cadena caiman 6 in Urrea 797UR</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>6</v>
+      </c>
+      <c r="H85" t="n">
+        <v>12</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>400</v>
+      </c>
+      <c r="K85" t="n">
+        <v>80</v>
+      </c>
+      <c r="L85" t="n">
+        <v>40</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TUB</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>FTS-TUB-01-C1-04</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>STILL1</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Llave stillson 14 in Husky 73126</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>6</v>
+      </c>
+      <c r="H86" t="n">
+        <v>104</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>356</v>
+      </c>
+      <c r="K86" t="n">
+        <v>83</v>
+      </c>
+      <c r="L86" t="n">
+        <v>32</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TUB</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>FTS-TUB-01-C2-01</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>STILL2</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Llave stillson 14 in Husky 73126</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>6</v>
+      </c>
+      <c r="H87" t="n">
+        <v>12</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>356</v>
+      </c>
+      <c r="K87" t="n">
+        <v>83</v>
+      </c>
+      <c r="L87" t="n">
+        <v>32</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TUB</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>FTS-TUB-01-C2-02</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>NIVTUB2</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Nivel para tuberia 6.5 in Milwaukee 48-22-5110</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>6</v>
+      </c>
+      <c r="H88" t="n">
+        <v>107</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>159</v>
+      </c>
+      <c r="K88" t="n">
+        <v>51</v>
+      </c>
+      <c r="L88" t="n">
+        <v>19</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8146,7 +14344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8968,7 +15166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10267,7 +16465,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10585,7 +16783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10700,7 +16898,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10991,7 +17189,6 @@
       <c r="C8" t="n">
         <v>4271</v>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>9 cajas</t>
@@ -11000,9 +17197,6 @@
       <c r="F8" t="n">
         <v>4271</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11017,7 +17211,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>2) 42 piezas cambiaron de medida con fuente documental (ver catalogo_maestro.xlsx, hoja Cambios_sesion_nocturna).</t>
@@ -11025,7 +17218,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>3) Regla nueva: las M18 y sus baterias van en un cajon con barra para candado. La 8420 no trae barra (fabricante) y solo se asegura desapilada (comprador HDUS).</t>
@@ -11033,7 +17225,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>4) Estrategia nueva "fijo": prueba todos los juegos de 1 a 3 cajas por modulo y elige el que mete todo con menos cajas, menos alto y al menos un cajon de reserva si se puede.</t>
@@ -11041,7 +17232,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>5) La segueta (475 mm segun HD MX, posible empaque) ya no cabe en ningun cajon: pasa a Sueltos hasta medirla.</t>
@@ -11053,7 +17243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11205,7 +17395,6 @@
           <t>si</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>PRES11, AJ12, NAVAJA, VERN, WIHA-PC, PDIAG, PELEC, AJ8, CHOF8</t>
@@ -11238,7 +17427,6 @@
           <t>si</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>ESM45, CARG1</t>
@@ -11345,7 +17533,6 @@
           <t>si</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>ESM45, IMP38, ROTO18, CARG1, BAT1, BAT2, IMP14</t>
@@ -11378,7 +17565,6 @@
           <t>si</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>CARG1, ROTO18, PELEC</t>
@@ -11411,7 +17597,6 @@
           <t>si</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>PRES11, AJ12, NAVAJA, VERN, WIHA-PC, PDIAG, PELEC, AJ8, CHOF8</t>
@@ -11444,7 +17629,6 @@
           <t>si</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>ESM45, CARG1</t>

--- a/docs/herramientas-mx/diseno_carrito.xlsx
+++ b/docs/herramientas-mx/diseno_carrito.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Acomodo_3D_vigente" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Acomodo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Estrategias" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Verificacion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sueltos" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Parametros" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Cambios_sesion_nocturna" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Comparacion_bases" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Huecos_individuales" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acomodo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Estrategias" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Verificacion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sueltos" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Parametros" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cambios_sesion_nocturna" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Comparacion_bases" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R88"/>
+  <dimension ref="A1:R89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,7 +533,7 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Posiciones vigentes tras el chequeo 3D de la sesion nocturna 2 (#338): scripts/interferencias_3d.py. Las otras hojas son las de la sesion 1.</t>
+          <t>Posiciones vigentes tras el chequeo 3D (#338) y las correcciones de #343 (juegos en huecos individuales, base 8410 + 8442).</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1339,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="H13" t="n">
         <v>12</v>
@@ -1408,7 +1409,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>255</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
         <v>12</v>
@@ -1422,7 +1423,7 @@
         <v>150</v>
       </c>
       <c r="K14" t="n">
-        <v>80</v>
+        <v>149.1</v>
       </c>
       <c r="L14" t="n">
         <v>20</v>
@@ -1478,10 +1479,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>223</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>166</v>
+        <v>235.1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1499,15 +1500,15 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PASA</t>
+          <t>PASA JUSTO</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>a herramienta vs fichas ajenas</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1548,10 +1549,10 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>168</v>
       </c>
       <c r="H16" t="n">
-        <v>166</v>
+        <v>104</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1618,10 +1619,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>196</v>
       </c>
       <c r="H17" t="n">
-        <v>234</v>
+        <v>235.1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1639,11 +1640,11 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>PASA JUSTO</t>
+          <t>PASA</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1691,7 +1692,7 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>104</v>
+        <v>173.1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1749,16 +1750,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MATR</t>
+          <t>MATRACA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Matraca 3/8 + dados (juego Husky P, 3/8)</t>
+          <t>Matraca rotativa 3/8 Husky H38ROTORATMX</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>291</v>
       </c>
       <c r="H19" t="n">
         <v>6</v>
@@ -1769,13 +1770,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>200</v>
+        <v>42</v>
       </c>
       <c r="K19" t="n">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="L19" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1783,16 +1784,16 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>b ficha vs cajon</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>solo lado 2</t>
+          <t>ambos</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1829,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>218</v>
+        <v>12</v>
       </c>
       <c r="H20" t="n">
         <v>6</v>
@@ -1853,11 +1854,11 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>b ficha vs cajon</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1898,21 +1899,21 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>218</v>
+        <v>345</v>
       </c>
       <c r="H21" t="n">
-        <v>263</v>
+        <v>6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J21" t="n">
+        <v>30</v>
+      </c>
+      <c r="K21" t="n">
         <v>190</v>
-      </c>
-      <c r="K21" t="n">
-        <v>30</v>
       </c>
       <c r="L21" t="n">
         <v>30</v>
@@ -1949,43 +1950,43 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C5-01</t>
+          <t>FTS-BAS-01-C4-04</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TAZON</t>
+          <t>DADOS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tazon magnetico Husky</t>
+          <t>Dadera: 29 dados de la caja P, cada uno en su hueco</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>248</v>
+        <v>199</v>
       </c>
       <c r="H22" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="K22" t="n">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="L22" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1993,7 +1994,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2024,21 +2025,21 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C5-02</t>
+          <t>FTS-BAS-01-C5-01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HDS-A</t>
+          <t>TAZON</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3 desarmadores Husky (P1, P1, P2)</t>
+          <t>Tazon magnetico Husky</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>248</v>
       </c>
       <c r="H23" t="n">
         <v>12</v>
@@ -2049,13 +2050,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="K23" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L23" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2067,7 +2068,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>d dedos lado 2</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2094,24 +2095,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C5-03</t>
+          <t>FTS-BAS-01-C5-02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>WIHA-DS2</t>
+          <t>HDS-A</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Desarmador aislado PH2 x 100 (32102)</t>
+          <t>3 desarmadores Husky (P1, P1, P2)</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>124</v>
+        <v>12</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2119,10 +2120,10 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="K24" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="L24" t="n">
         <v>32</v>
@@ -2137,7 +2138,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>d dedos lado 2</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2164,24 +2165,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C5-04</t>
+          <t>FTS-BAS-01-C5-03</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PRES6C</t>
+          <t>WIHA-DS2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pinza de presion C 6 in Torque Lock 48-22-3532</t>
+          <t>Desarmador aislado PH2 x 100 (32102)</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>168</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>174</v>
+        <v>124</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2189,13 +2190,13 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="K25" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="L25" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2234,21 +2235,21 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C5-05</t>
+          <t>FTS-BAS-01-C5-04</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FLEX1</t>
+          <t>PRES6C</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Flexometro 5 m Stanley 30-615</t>
+          <t>Pinza de presion C 6 in Torque Lock 48-22-3532</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>332</v>
+        <v>168</v>
       </c>
       <c r="H26" t="n">
         <v>174</v>
@@ -2259,13 +2260,13 @@
         </is>
       </c>
       <c r="J26" t="n">
+        <v>152</v>
+      </c>
+      <c r="K26" t="n">
         <v>70</v>
       </c>
-      <c r="K26" t="n">
-        <v>60</v>
-      </c>
       <c r="L26" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2273,7 +2274,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2304,21 +2305,21 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C5-06</t>
+          <t>FTS-BAS-01-C5-05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ESCAL</t>
+          <t>FLEX1</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Juego 3 brocas escalonadas Truper</t>
+          <t>Flexometro 5 m Stanley 30-615</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>332</v>
       </c>
       <c r="H27" t="n">
         <v>174</v>
@@ -2329,13 +2330,13 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="K27" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="L27" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2343,11 +2344,11 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>b ficha vs cajon</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2374,24 +2375,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C5-07</t>
+          <t>FTS-BAS-01-C5-06</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FLEX2</t>
+          <t>ESCAL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Flexometro 5 m Stanley 30-615</t>
+          <t>Juego 3 brocas escalonadas Truper</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>332</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>246</v>
+        <v>174</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2399,13 +2400,13 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="K28" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="L28" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2413,11 +2414,11 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>d dedos lado 2</t>
+          <t>b ficha vs cajon</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2444,24 +2445,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C5-08</t>
+          <t>FTS-BAS-01-C5-07</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>WIHA-DS4</t>
+          <t>FLEX2</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Desarmador aislado plano 4.5 x 100 (32023)</t>
+          <t>Flexometro 5 m Stanley 30-615</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>332</v>
       </c>
       <c r="H29" t="n">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2469,13 +2470,13 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>215</v>
+        <v>70</v>
       </c>
       <c r="K29" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="L29" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2487,7 +2488,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>d dedos lado 2</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2509,43 +2510,43 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C6-01</t>
+          <t>FTS-BAS-01-C5-08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HDS-B</t>
+          <t>WIHA-DS4</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3 desarmadores Husky (P2 x3)</t>
+          <t>Desarmador aislado plano 4.5 x 100 (32023)</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>276</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>100</v>
+        <v>215</v>
       </c>
       <c r="K30" t="n">
-        <v>230</v>
+        <v>30</v>
       </c>
       <c r="L30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2553,16 +2554,16 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>b ficha vs cajon</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>solo lado 2</t>
+          <t>ambos</t>
         </is>
       </c>
     </row>
@@ -2584,38 +2585,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C6-02</t>
+          <t>FTS-BAS-01-C6-01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PRES11</t>
+          <t>HDS-B</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pinza de presion C 11 in Torque Lock 48-22-3531</t>
+          <t>3 desarmadores Husky (P2 x3)</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>118</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
         <v>6</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>279</v>
+        <v>100</v>
       </c>
       <c r="K31" t="n">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="L31" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2623,11 +2624,11 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>d dedos lado 2</t>
+          <t>b ficha vs cajon</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2654,24 +2655,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C6-03</t>
+          <t>FTS-BAS-01-C6-02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>EXTS</t>
+          <t>PRES11</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Extensiones 3/8 (6 in, 10 in, oscilantes) y palanca</t>
+          <t>Pinza de presion C 11 in Torque Lock 48-22-3531</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>118</v>
       </c>
       <c r="H32" t="n">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2679,10 +2680,10 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="K32" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="L32" t="n">
         <v>25</v>
@@ -2697,12 +2698,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>d dedos lado 2</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>ambos</t>
+          <t>solo lado 2</t>
         </is>
       </c>
     </row>
@@ -2724,24 +2725,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C6-04</t>
+          <t>FTS-BAS-01-C6-03</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PREC6</t>
+          <t>EXTS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Juego 6 desarmadores de precision 48-22-2606 (estuche)</t>
+          <t>Extensiones 3/8 (6 in, 10 in, oscilantes) y palanca</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>118</v>
       </c>
       <c r="H33" t="n">
-        <v>220</v>
+        <v>128</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2749,10 +2750,10 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="K33" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L33" t="n">
         <v>25</v>
@@ -2772,7 +2773,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>solo lado 1</t>
+          <t>ambos</t>
         </is>
       </c>
     </row>
@@ -2794,21 +2795,21 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C6-05</t>
+          <t>FTS-BAS-01-C6-04</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ADAP</t>
+          <t>PREC6</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Juego 3 adaptadores 1/4-3/8-1/2</t>
+          <t>Juego 6 desarmadores de precision 48-22-2606 (estuche)</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>320</v>
+        <v>118</v>
       </c>
       <c r="H34" t="n">
         <v>220</v>
@@ -2819,10 +2820,10 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="K34" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="L34" t="n">
         <v>25</v>
@@ -2842,7 +2843,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>ambos</t>
+          <t>solo lado 1</t>
         </is>
       </c>
     </row>
@@ -2859,29 +2860,29 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C7-01</t>
+          <t>FTS-BAS-01-C6-05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MART</t>
+          <t>ADAP</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Martillo una curva 16 oz Truper MA-16F</t>
+          <t>Juego 3 adaptadores 1/4-3/8-1/2</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>320</v>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>220</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2889,13 +2890,13 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>340</v>
+        <v>70</v>
       </c>
       <c r="K35" t="n">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="L35" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2903,16 +2904,16 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>d dedos lado 2</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>solo lado 2</t>
+          <t>ambos</t>
         </is>
       </c>
     </row>
@@ -2934,38 +2935,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C7-02</t>
+          <t>FTS-BAS-01-C7-01</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>WIHA-DS3</t>
+          <t>MART</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Desarmador aislado plano 3.0 x 100 (32012)</t>
+          <t>Martillo una curva 16 oz Truper MA-16F</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>358</v>
+        <v>6</v>
       </c>
       <c r="H36" t="n">
         <v>6</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>28</v>
+        <v>340</v>
       </c>
       <c r="K36" t="n">
-        <v>205</v>
+        <v>130</v>
       </c>
       <c r="L36" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2973,16 +2974,16 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>d dedos lado 2</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>ambos</t>
+          <t>solo lado 2</t>
         </is>
       </c>
     </row>
@@ -3004,38 +3005,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C7-03</t>
+          <t>FTS-BAS-01-C7-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PRES7</t>
+          <t>WIHA-DS3</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pinza de presion 7 in mordaza recta Husky</t>
+          <t>Desarmador aislado plano 3.0 x 100 (32012)</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>358</v>
+      </c>
+      <c r="H37" t="n">
         <v>6</v>
       </c>
-      <c r="H37" t="n">
-        <v>148</v>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>182</v>
+        <v>28</v>
       </c>
       <c r="K37" t="n">
-        <v>62</v>
+        <v>205</v>
       </c>
       <c r="L37" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3074,38 +3075,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C7-04</t>
+          <t>FTS-BAS-01-C7-03</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WIHA-PP</t>
+          <t>PRES7</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pinza de punta aislada 160 (32926)</t>
+          <t>Pinza de presion 7 in mordaza recta Husky</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>272</v>
+        <v>6</v>
       </c>
       <c r="H38" t="n">
         <v>148</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="K38" t="n">
-        <v>160</v>
+        <v>62</v>
       </c>
       <c r="L38" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3144,38 +3145,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C7-05</t>
+          <t>FTS-BAS-01-C7-04</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PRES10</t>
+          <t>WIHA-PP</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pinza de presion 10 in mordaza curva Husky 709204</t>
+          <t>Pinza de punta aislada 160 (32926)</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>272</v>
       </c>
       <c r="H39" t="n">
-        <v>223</v>
+        <v>148</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>254</v>
+        <v>55</v>
       </c>
       <c r="K39" t="n">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="L39" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3183,11 +3184,11 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>b ficha vs cajon</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3204,34 +3205,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>48-22-8420</t>
+          <t>48-22-8444</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C8-01</t>
+          <t>FTS-BAS-01-C7-05</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ESM45</t>
+          <t>PRES10</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mini esmeriladora 4-1/2 alambrica 6130-33 + cable</t>
+          <t>Pinza de presion 10 in mordaza curva Husky 709204</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>12</v>
+        <v>223</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3239,13 +3240,13 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>357</v>
+        <v>254</v>
       </c>
       <c r="K40" t="n">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="L40" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3253,11 +3254,11 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>b ficha vs cajon</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3274,27 +3275,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>48-22-8420</t>
+          <t>48-22-8442</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FTS-BAS-01-C9-01</t>
+          <t>FTS-BAS-01-C8-01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CARG1</t>
+          <t>ESM45</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cargador sencillo M18/M12 48-59-1812 (compra)</t>
+          <t>Mini esmeriladora 4-1/2 alambrica 6130-33 + cable</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -3309,13 +3310,13 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>202</v>
+        <v>357</v>
       </c>
       <c r="K41" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="L41" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3339,53 +3340,53 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ELE</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>48-22-8444</t>
+          <t>48-22-8442</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FTS-ELE-01-C1-01</t>
+          <t>FTS-BAS-01-C9-01</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>EXTECH</t>
+          <t>CARG1</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Amperimetro Extech MA440</t>
+          <t>Cargador sencillo M18/M12 48-59-1812 (compra)</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>70</v>
+        <v>202</v>
       </c>
       <c r="K42" t="n">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="L42" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3393,16 +3394,16 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>b ficha vs cajon</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>solo lado 2</t>
+          <t>ambos</t>
         </is>
       </c>
     </row>
@@ -3424,21 +3425,21 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FTS-ELE-01-C1-02</t>
+          <t>FTS-ELE-01-C1-01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>DETV</t>
+          <t>EXTECH</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Detector de voltaje Milwaukee</t>
+          <t>Amperimetro Extech MA440</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="H43" t="n">
         <v>6</v>
@@ -3449,13 +3450,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="K43" t="n">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="L43" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3463,16 +3464,16 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>b ficha vs cajon</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>ambos</t>
+          <t>solo lado 2</t>
         </is>
       </c>
     </row>
@@ -3494,38 +3495,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FTS-ELE-01-C1-03</t>
+          <t>FTS-ELE-01-C1-02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FLUKE</t>
+          <t>DETV</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pinza amperimetrica Fluke 302+</t>
+          <t>Detector de voltaje Milwaukee</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="H44" t="n">
         <v>6</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>207</v>
+        <v>25</v>
       </c>
       <c r="K44" t="n">
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="L44" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3537,12 +3538,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>d dedos lado 2</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>solo lado 2</t>
+          <t>ambos</t>
         </is>
       </c>
     </row>
@@ -3564,24 +3565,24 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FTS-ELE-01-C1-04</t>
+          <t>FTS-ELE-01-C1-03</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HDS-C</t>
+          <t>FLUKE</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>3 desarmadores Husky 1/4</t>
+          <t>Pinza amperimetrica Fluke 302+</t>
         </is>
       </c>
       <c r="G45" t="n">
         <v>148</v>
       </c>
       <c r="H45" t="n">
-        <v>93</v>
+        <v>6</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3589,13 +3590,13 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>250</v>
+        <v>207</v>
       </c>
       <c r="K45" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L45" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -3607,12 +3608,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>d dedos lado 2</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>ambos</t>
+          <t>solo lado 2</t>
         </is>
       </c>
     </row>
@@ -3634,24 +3635,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FTS-ELE-01-C1-05</t>
+          <t>FTS-ELE-01-C1-04</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HDS-D</t>
+          <t>HDS-C</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3 desarmadores Husky 1/4, 3/16</t>
+          <t>3 desarmadores Husky 1/4</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>148</v>
       </c>
       <c r="H46" t="n">
-        <v>205</v>
+        <v>93</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3704,24 +3705,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FTS-ELE-01-C1-06</t>
+          <t>FTS-ELE-01-C1-05</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SACAB</t>
+          <t>HDS-D</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>3 sacabocados Dogo 7, 13 y 19 mm</t>
+          <t>3 desarmadores Husky 1/4, 3/16</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>6</v>
+        <v>148</v>
       </c>
       <c r="H47" t="n">
-        <v>216.5</v>
+        <v>205</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3729,13 +3730,13 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="K47" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="L47" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -3743,11 +3744,11 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>d dedos lado 2</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -3769,29 +3770,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FTS-ELE-01-C2-01</t>
+          <t>FTS-ELE-01-C1-06</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CRIMP</t>
+          <t>SACAB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pinza crimpadora Weidmuller 1445070000</t>
+          <t>3 sacabocados Dogo 7, 13 y 19 mm</t>
         </is>
       </c>
       <c r="G48" t="n">
         <v>6</v>
       </c>
       <c r="H48" t="n">
-        <v>12</v>
+        <v>216.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3799,13 +3800,13 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="K48" t="n">
         <v>90</v>
       </c>
       <c r="L48" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -3813,7 +3814,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3844,24 +3845,24 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FTS-ELE-01-C2-02</t>
+          <t>FTS-ELE-01-C2-01</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PONCH</t>
+          <t>CRIMP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pinza ponchadora RJ45</t>
+          <t>Pinza crimpadora Weidmuller 1445070000</t>
         </is>
       </c>
       <c r="G49" t="n">
         <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3869,13 +3870,13 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="K49" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="L49" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -3887,7 +3888,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>d dedos lado 2</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -3914,21 +3915,21 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FTS-ELE-01-C2-03</t>
+          <t>FTS-ELE-01-C2-02</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PELA</t>
+          <t>PONCH</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pelacables Commercial Electric CE100821</t>
+          <t>Pinza ponchadora RJ45</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>218</v>
+        <v>6</v>
       </c>
       <c r="H50" t="n">
         <v>114</v>
@@ -3939,25 +3940,25 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="K50" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="L50" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>PASA</t>
+          <t>PASA JUSTO</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>a herramienta vs fichas ajenas</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -3984,24 +3985,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FTS-ELE-01-C2-04</t>
+          <t>FTS-ELE-01-C2-03</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MAPPER</t>
+          <t>PELA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Probador de cableado Fluke MicroMapper MT-8200-49A</t>
+          <t>Pelacables Commercial Electric CE100821</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="H51" t="n">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -4009,25 +4010,25 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="K51" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L51" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>PASA JUSTO</t>
+          <t>PASA</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>a herramienta vs fichas ajenas</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4039,53 +4040,53 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>ELE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>48-22-8447</t>
+          <t>48-22-8444</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C1-01</t>
+          <t>FTS-ELE-01-C2-04</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>EXTQ</t>
+          <t>MAPPER</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Extractor de quijadas 6 t Urrea 4216</t>
+          <t>Probador de cableado Fluke MicroMapper MT-8200-49A</t>
         </is>
       </c>
       <c r="G52" t="n">
+        <v>248</v>
+      </c>
+      <c r="H52" t="n">
         <v>12</v>
       </c>
-      <c r="H52" t="n">
-        <v>6</v>
-      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="K52" t="n">
-        <v>300</v>
+        <v>52</v>
       </c>
       <c r="L52" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4124,21 +4125,21 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C1-02</t>
+          <t>FTS-SOL-01-C1-01</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PRES10B</t>
+          <t>EXTQ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pinza de presion 10 in curva (2a)</t>
+          <t>Extractor de quijadas 6 t Urrea 4216</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>306</v>
+        <v>12</v>
       </c>
       <c r="H53" t="n">
         <v>6</v>
@@ -4149,13 +4150,13 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="K53" t="n">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="L53" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -4194,21 +4195,21 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C1-03</t>
+          <t>FTS-SOL-01-C1-02</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PRES11B</t>
+          <t>PRES10B</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pinza de presion C 11 in (2a)</t>
+          <t>Pinza de presion 10 in curva (2a)</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>184</v>
+        <v>306</v>
       </c>
       <c r="H54" t="n">
         <v>6</v>
@@ -4219,13 +4220,13 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="K54" t="n">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="L54" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -4264,21 +4265,21 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C1-04</t>
+          <t>FTS-SOL-01-C1-03</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FRESA</t>
+          <t>PRES11B</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fresa de carburo SF-5</t>
+          <t>Pinza de presion C 11 in (2a)</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>384</v>
+        <v>184</v>
       </c>
       <c r="H55" t="n">
         <v>6</v>
@@ -4289,13 +4290,13 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="K55" t="n">
-        <v>70</v>
+        <v>279</v>
       </c>
       <c r="L55" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -4329,43 +4330,43 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C2-01</t>
+          <t>FTS-SOL-01-C1-04</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MACH</t>
+          <t>FRESA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Juego 40 machuelos y tarrajas Truper 11442 (2 estuches)</t>
+          <t>Fresa de carburo SF-5</t>
         </is>
       </c>
       <c r="G56" t="n">
+        <v>384</v>
+      </c>
+      <c r="H56" t="n">
         <v>6</v>
       </c>
-      <c r="H56" t="n">
-        <v>11.5</v>
-      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>330</v>
+        <v>15</v>
       </c>
       <c r="K56" t="n">
-        <v>290</v>
+        <v>70</v>
       </c>
       <c r="L56" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -4373,7 +4374,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -4404,46 +4405,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C2-02</t>
+          <t>FTS-SOL-01-C2-01</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TORX</t>
+          <t>MACH</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Juego llaves Torx/hex tipo navaja Husky</t>
+          <t>Juego 40 machuelos y tarrajas Truper 11442 (2 estuches)</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>348</v>
+        <v>6</v>
       </c>
       <c r="H57" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J57" t="n">
+        <v>330</v>
+      </c>
+      <c r="K57" t="n">
+        <v>290</v>
+      </c>
+      <c r="L57" t="n">
         <v>45</v>
       </c>
-      <c r="K57" t="n">
-        <v>130</v>
-      </c>
-      <c r="L57" t="n">
-        <v>30</v>
-      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>PASA JUSTO</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -4474,24 +4475,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C2-03</t>
+          <t>FTS-SOL-01-C2-02</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EXTOR</t>
+          <t>TORX</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Juego 5 extractores de tornillos Truper EXT-5</t>
+          <t>Juego llaves Torx/hex tipo navaja Husky</t>
         </is>
       </c>
       <c r="G58" t="n">
         <v>348</v>
       </c>
       <c r="H58" t="n">
-        <v>148</v>
+        <v>6</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -4499,13 +4500,13 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="K58" t="n">
         <v>130</v>
       </c>
       <c r="L58" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -4522,7 +4523,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>solo lado 1</t>
+          <t>ambos</t>
         </is>
       </c>
     </row>
@@ -4539,43 +4540,43 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C3-01</t>
+          <t>FTS-SOL-01-C2-03</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ESM45B</t>
+          <t>EXTOR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mini esmeriladora 4-1/2 6130-33 (2a)</t>
+          <t>Juego 5 extractores de tornillos Truper EXT-5</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>6</v>
+        <v>348</v>
       </c>
       <c r="H59" t="n">
-        <v>12</v>
+        <v>148</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>357</v>
+        <v>60</v>
       </c>
       <c r="K59" t="n">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="L59" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -4592,7 +4593,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>ambos</t>
+          <t>solo lado 1</t>
         </is>
       </c>
     </row>
@@ -4614,24 +4615,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C3-02</t>
+          <t>FTS-SOL-01-C3-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ESCMAG</t>
+          <t>ESM45B</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>4 escuadras magneticas 4 in Truper (apiladas)</t>
+          <t>Mini esmeriladora 4-1/2 6130-33 (2a)</t>
         </is>
       </c>
       <c r="G60" t="n">
         <v>6</v>
       </c>
       <c r="H60" t="n">
-        <v>176</v>
+        <v>12</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -4639,13 +4640,13 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>150</v>
+        <v>357</v>
       </c>
       <c r="K60" t="n">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="L60" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -4653,11 +4654,11 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>b ficha vs cajon</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -4679,29 +4680,29 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C4-01</t>
+          <t>FTS-SOL-01-C3-02</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>COMB10</t>
+          <t>ESCMAG</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Juego 10 llaves combinadas Husky BITE</t>
+          <t>4 escuadras magneticas 4 in Truper (apiladas)</t>
         </is>
       </c>
       <c r="G61" t="n">
         <v>6</v>
       </c>
       <c r="H61" t="n">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -4709,13 +4710,13 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="K61" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="L61" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -4723,11 +4724,11 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>d dedos lado 2</t>
+          <t>b ficha vs cajon</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -4754,24 +4755,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C4-02</t>
+          <t>FTS-SOL-01-C4-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PRES7B</t>
+          <t>COMB10</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pinza de presion 7 in (2a, hoy faltante)</t>
+          <t>Juego 10 llaves combinadas Husky BITE</t>
         </is>
       </c>
       <c r="G62" t="n">
         <v>6</v>
       </c>
       <c r="H62" t="n">
-        <v>204</v>
+        <v>12</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4779,13 +4780,13 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>182</v>
+        <v>300</v>
       </c>
       <c r="K62" t="n">
-        <v>62</v>
+        <v>180</v>
       </c>
       <c r="L62" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -4797,7 +4798,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>d dedos lado 2</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -4824,21 +4825,21 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C4-03</t>
+          <t>FTS-SOL-01-C4-02</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PRES6CB</t>
+          <t>PRES7B</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pinza de presion C 6 in (2a)</t>
+          <t>Pinza de presion 7 in (2a, hoy faltante)</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="H63" t="n">
         <v>204</v>
@@ -4849,13 +4850,13 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="K63" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="L63" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -4889,29 +4890,29 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C5-01</t>
+          <t>FTS-SOL-01-C4-03</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>LIMAS</t>
+          <t>PRES6CB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>3 limas 6 in (redonda, media cana, triangular)</t>
+          <t>Pinza de presion C 6 in (2a)</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="H64" t="n">
-        <v>12</v>
+        <v>204</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -4919,13 +4920,13 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>250</v>
+        <v>152</v>
       </c>
       <c r="K64" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L64" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -4959,22 +4960,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C6-01</t>
+          <t>FTS-SOL-01-C5-01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MOTO</t>
+          <t>LIMAS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Moto tool Truper (estuche)</t>
+          <t>3 limas 6 in (redonda, media cana, triangular)</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -4989,13 +4990,13 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="K65" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="L65" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -5034,24 +5035,24 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FTS-SOL-01-C6-02</t>
+          <t>FTS-SOL-01-C6-01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RECT</t>
+          <t>MOTO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rectificador DeWalt DWE4887</t>
+          <t>Moto tool Truper (estuche)</t>
         </is>
       </c>
       <c r="G66" t="n">
         <v>6</v>
       </c>
       <c r="H66" t="n">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5059,13 +5060,13 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="K66" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="L66" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -5073,11 +5074,11 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>b ficha vs cajon</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -5089,39 +5090,39 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>48-22-8442</t>
+          <t>48-22-8447</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FTS-CIV-01-C1-01</t>
+          <t>FTS-SOL-01-C6-02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>TAL12</t>
+          <t>RECT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Taladro percutor alambrico 1/2 5375-20</t>
+          <t>Rectificador DeWalt DWE4887</t>
         </is>
       </c>
       <c r="G67" t="n">
         <v>6</v>
       </c>
       <c r="H67" t="n">
-        <v>12</v>
+        <v>224</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5129,13 +5130,13 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="K67" t="n">
-        <v>265</v>
+        <v>70</v>
       </c>
       <c r="L67" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -5143,11 +5144,11 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>b ficha vs cajon</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -5169,22 +5170,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>FTS-CIV-01-C2-01</t>
+          <t>FTS-CIV-01-C1-01</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SDS</t>
+          <t>TAL12</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rotomartillo SDS-Plus 5485-21 (sin estuche)</t>
+          <t>Taladro percutor alambrico 1/2 5375-20</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -5199,13 +5200,13 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="K68" t="n">
-        <v>195</v>
+        <v>265</v>
       </c>
       <c r="L68" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -5244,24 +5245,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>FTS-CIV-01-C2-02</t>
+          <t>FTS-CIV-01-C2-01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MANGOS</t>
+          <t>SDS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2 mangos laterales</t>
+          <t>Rotomartillo SDS-Plus 5485-21 (sin estuche)</t>
         </is>
       </c>
       <c r="G69" t="n">
         <v>6</v>
       </c>
       <c r="H69" t="n">
-        <v>219</v>
+        <v>12</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5269,13 +5270,13 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>200</v>
+        <v>335</v>
       </c>
       <c r="K69" t="n">
-        <v>60</v>
+        <v>195</v>
       </c>
       <c r="L69" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -5283,11 +5284,11 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>b ficha vs cajon</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -5304,34 +5305,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>48-22-8444</t>
+          <t>48-22-8442</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FTS-CIV-01-C3-01</t>
+          <t>FTS-CIV-01-C2-02</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SDSBIT</t>
+          <t>MANGOS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Juego 15 brocas y cinceles SDS-Plus DeWalt DWA0870</t>
+          <t>2 mangos laterales</t>
         </is>
       </c>
       <c r="G70" t="n">
         <v>6</v>
       </c>
       <c r="H70" t="n">
-        <v>12</v>
+        <v>219</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5339,13 +5340,13 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="K70" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="L70" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -5353,11 +5354,11 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>b ficha vs cajon</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -5379,22 +5380,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>FTS-CIV-01-C4-01</t>
+          <t>FTS-CIV-01-C3-01</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MART2</t>
+          <t>SDSBIT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Martillo una curva 16 oz (2o)</t>
+          <t>Juego 15 brocas y cinceles SDS-Plus DeWalt DWA0870</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -5409,13 +5410,13 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="K71" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="L71" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -5427,7 +5428,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>d dedos lado 2</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -5454,24 +5455,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FTS-CIV-01-C4-02</t>
+          <t>FTS-CIV-01-C4-01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>MART2</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2 cinceles de corte frio 5/16x6 y 7/8x10</t>
+          <t>Martillo una curva 16 oz (2o)</t>
         </is>
       </c>
       <c r="G72" t="n">
         <v>6</v>
       </c>
       <c r="H72" t="n">
-        <v>154</v>
+        <v>12</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5479,13 +5480,13 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>254</v>
+        <v>340</v>
       </c>
       <c r="K72" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="L72" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -5497,7 +5498,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>d dedos lado 2</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -5514,48 +5515,48 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>48-22-8420</t>
+          <t>48-22-8444</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>FTS-CIV-01-C7-01</t>
+          <t>FTS-CIV-01-C4-02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>LIJA</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lijadora orbital M18 2648-20</t>
+          <t>2 cinceles de corte frio 5/16x6 y 7/8x10</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>260</v>
+        <v>6</v>
       </c>
       <c r="H73" t="n">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>146</v>
+        <v>254</v>
       </c>
       <c r="K73" t="n">
-        <v>267</v>
+        <v>60</v>
       </c>
       <c r="L73" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -5563,11 +5564,11 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>b ficha vs cajon</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -5594,21 +5595,21 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>FTS-CIV-01-C7-02</t>
+          <t>FTS-CIV-01-C7-01</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CALAD</t>
+          <t>LIJA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sierra caladora Ryobi JS481LG</t>
+          <t>Lijadora orbital M18 2648-20</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>12</v>
+        <v>260</v>
       </c>
       <c r="H74" t="n">
         <v>6</v>
@@ -5619,13 +5620,13 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>236</v>
+        <v>146</v>
       </c>
       <c r="K74" t="n">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="L74" t="n">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -5633,11 +5634,11 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>b ficha vs cajon</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -5659,43 +5660,43 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>FTS-CIV-01-C8-01</t>
+          <t>FTS-CIV-01-C7-02</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MAZO</t>
+          <t>CALAD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mazo de hule 16 oz Truper MH-16</t>
+          <t>Sierra caladora Ryobi JS481LG</t>
         </is>
       </c>
       <c r="G75" t="n">
+        <v>12</v>
+      </c>
+      <c r="H75" t="n">
         <v>6</v>
       </c>
-      <c r="H75" t="n">
-        <v>12</v>
-      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>357</v>
+        <v>236</v>
       </c>
       <c r="K75" t="n">
-        <v>104</v>
+        <v>279</v>
       </c>
       <c r="L75" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -5719,65 +5720,65 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>48-22-8442</t>
+          <t>48-22-8420</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>FTS-MED-01-C1-01</t>
+          <t>FTS-CIV-01-C8-01</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LASER</t>
+          <t>MAZO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nivel laser verde Bosch GLL 12-22 G</t>
+          <t>Mazo de hule 16 oz Truper MH-16</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>157</v>
+        <v>6</v>
       </c>
       <c r="H76" t="n">
-        <v>198</v>
+        <v>12</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>64</v>
+        <v>357</v>
       </c>
       <c r="K76" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L76" t="n">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>PASA</t>
+          <t>PASA JUSTO</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>d dedos lado 2</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -5804,24 +5805,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>FTS-MED-01-C1-02</t>
+          <t>FTS-MED-01-C1-01</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AMARRE</t>
+          <t>LASER</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>4 amarres tipo matraca 3.6 m (enrollados)</t>
+          <t>Nivel laser verde Bosch GLL 12-22 G</t>
         </is>
       </c>
       <c r="G77" t="n">
         <v>157</v>
       </c>
       <c r="H77" t="n">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -5829,25 +5830,25 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="K77" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="L77" t="n">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>PASA JUSTO</t>
+          <t>PASA</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>b ficha vs cajon</t>
+          <t>d dedos lado 2</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -5874,21 +5875,21 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>FTS-MED-01-C1-03</t>
+          <t>FTS-MED-01-C1-02</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ESCCOMB</t>
+          <t>AMARRE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Escuadra combinada 12 in Empire 220IM</t>
+          <t>4 amarres tipo matraca 3.6 m (enrollados)</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="H78" t="n">
         <v>6</v>
@@ -5899,13 +5900,13 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="K78" t="n">
-        <v>304</v>
+        <v>180</v>
       </c>
       <c r="L78" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -5913,11 +5914,11 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>d dedos lado 2</t>
+          <t>b ficha vs cajon</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -5944,24 +5945,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>FTS-MED-01-C1-04</t>
+          <t>FTS-MED-01-C1-03</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>LASER2</t>
+          <t>ESCCOMB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nivel laser verde Bosch (2o)</t>
+          <t>Escuadra combinada 12 in Empire 220IM</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>233</v>
+        <v>12</v>
       </c>
       <c r="H79" t="n">
-        <v>198</v>
+        <v>6</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -5969,25 +5970,25 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="K79" t="n">
-        <v>100</v>
+        <v>304</v>
       </c>
       <c r="L79" t="n">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>PASA</t>
+          <t>PASA JUSTO</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>d dedos lado 2</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -6014,24 +6015,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>FTS-MED-01-C1-05</t>
+          <t>FTS-MED-01-C1-04</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>GRILL</t>
+          <t>LASER2</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>3 grilletes 5/8 Crosby</t>
+          <t>Nivel laser verde Bosch (2o)</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>289</v>
+        <v>233</v>
       </c>
       <c r="H80" t="n">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -6039,25 +6040,25 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="K80" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="L80" t="n">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>PASA JUSTO</t>
+          <t>PASA</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>b ficha vs cajon</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -6079,55 +6080,55 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>FTS-MED-01-C2-01</t>
+          <t>FTS-MED-01-C1-05</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>TORPEDO2</t>
+          <t>GRILL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nivel torpedo magnetico 9 in (2o)</t>
+          <t>3 grilletes 5/8 Crosby</t>
         </is>
       </c>
       <c r="G81" t="n">
+        <v>289</v>
+      </c>
+      <c r="H81" t="n">
         <v>6</v>
       </c>
-      <c r="H81" t="n">
-        <v>190</v>
-      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>230</v>
+        <v>90</v>
       </c>
       <c r="K81" t="n">
+        <v>130</v>
+      </c>
+      <c r="L81" t="n">
         <v>45</v>
       </c>
-      <c r="L81" t="n">
-        <v>16</v>
-      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>PASA JUSTO</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>b ficha vs cajon</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -6154,24 +6155,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>FTS-MED-01-C2-02</t>
+          <t>FTS-MED-01-C2-01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ESCCAR</t>
+          <t>TORPEDO2</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Escuadra de carpintero 12 in Truper EC-12</t>
+          <t>Nivel torpedo magnetico 9 in (2o)</t>
         </is>
       </c>
       <c r="G82" t="n">
         <v>6</v>
       </c>
       <c r="H82" t="n">
-        <v>12</v>
+        <v>190</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -6179,13 +6180,13 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>304</v>
+        <v>230</v>
       </c>
       <c r="K82" t="n">
-        <v>166</v>
+        <v>45</v>
       </c>
       <c r="L82" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -6197,7 +6198,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>d dedos lado 2</t>
+          <t>d dedos lado 1</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -6209,39 +6210,39 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TUB</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>48-22-8443</t>
+          <t>48-22-8442</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>FTS-TUB-01-C1-01</t>
+          <t>FTS-MED-01-C2-02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CAB34</t>
+          <t>ESCCAR</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cabezal 12R 3/4 NPT de repuesto</t>
+          <t>Escuadra de carpintero 12 in Truper EC-12</t>
         </is>
       </c>
       <c r="G83" t="n">
         <v>6</v>
       </c>
       <c r="H83" t="n">
-        <v>199</v>
+        <v>12</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6249,13 +6250,13 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>100</v>
+        <v>304</v>
       </c>
       <c r="K83" t="n">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="L83" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -6263,11 +6264,11 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>b ficha vs cajon</t>
+          <t>d dedos lado 2</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -6294,21 +6295,21 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>FTS-TUB-01-C1-02</t>
+          <t>FTS-TUB-01-C1-01</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>NIVTUB1</t>
+          <t>CAB34</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nivel para tuberia 6.5 in Milwaukee 48-22-5110</t>
+          <t>Cabezal 12R 3/4 NPT de repuesto</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>118</v>
+        <v>6</v>
       </c>
       <c r="H84" t="n">
         <v>199</v>
@@ -6319,13 +6320,13 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="K84" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="L84" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -6333,11 +6334,11 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>d dedos lado 1</t>
+          <t>b ficha vs cajon</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -6364,24 +6365,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>FTS-TUB-01-C1-03</t>
+          <t>FTS-TUB-01-C1-02</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CAIMAN</t>
+          <t>NIVTUB1</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Llave de cadena caiman 6 in Urrea 797UR</t>
+          <t>Nivel para tuberia 6.5 in Milwaukee 48-22-5110</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>6</v>
+        <v>118</v>
       </c>
       <c r="H85" t="n">
-        <v>12</v>
+        <v>199</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6389,13 +6390,13 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>400</v>
+        <v>159</v>
       </c>
       <c r="K85" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="L85" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -6434,24 +6435,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>FTS-TUB-01-C1-04</t>
+          <t>FTS-TUB-01-C1-03</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>STILL1</t>
+          <t>CAIMAN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Llave stillson 14 in Husky 73126</t>
+          <t>Llave de cadena caiman 6 in Urrea 797UR</t>
         </is>
       </c>
       <c r="G86" t="n">
         <v>6</v>
       </c>
       <c r="H86" t="n">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -6459,13 +6460,13 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>356</v>
+        <v>400</v>
       </c>
       <c r="K86" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L86" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -6499,17 +6500,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>FTS-TUB-01-C2-01</t>
+          <t>FTS-TUB-01-C1-04</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>STILL2</t>
+          <t>STILL1</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6521,7 +6522,7 @@
         <v>6</v>
       </c>
       <c r="H87" t="n">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6574,24 +6575,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>FTS-TUB-01-C2-02</t>
+          <t>FTS-TUB-01-C2-01</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>NIVTUB2</t>
+          <t>STILL2</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nivel para tuberia 6.5 in Milwaukee 48-22-5110</t>
+          <t>Llave stillson 14 in Husky 73126</t>
         </is>
       </c>
       <c r="G88" t="n">
         <v>6</v>
       </c>
       <c r="H88" t="n">
-        <v>107</v>
+        <v>12</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -6599,13 +6600,13 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>159</v>
+        <v>356</v>
       </c>
       <c r="K88" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="L88" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -6621,6 +6622,76 @@
         </is>
       </c>
       <c r="P88" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TUB</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>48-22-8443</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>FTS-TUB-01-C2-02</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>NIVTUB2</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Nivel para tuberia 6.5 in Milwaukee 48-22-5110</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>6</v>
+      </c>
+      <c r="H89" t="n">
+        <v>107</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>159</v>
+      </c>
+      <c r="K89" t="n">
+        <v>51</v>
+      </c>
+      <c r="L89" t="n">
+        <v>19</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>PASA JUSTO</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>1</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>d dedos lado 1</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
         <is>
           <t>ambos</t>
         </is>
@@ -6632,6 +6703,3485 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>modulo</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>cajon</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>ficha</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>activo del hueco</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>pieza</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>forma</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>x en cajon</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>y en cajon</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>alto de la pieza</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>sku Home Depot</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Broca HSS 1/16 in</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="n">
+        <v>150</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-02</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Broca HSS 3/32 in</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>150</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-03</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Broca HSS 1/8 in</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I4" t="n">
+        <v>150</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-04</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Broca HSS 5/32 in</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>150</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Broca HSS 3/16 in</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>150</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-06</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Broca HSS 7/32 in</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>43</v>
+      </c>
+      <c r="I7" t="n">
+        <v>150</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-07</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Broca HSS 1/4 in</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>150</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-08</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Broca HSS 9/32 in</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>150</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-09</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Broca HSS 5/16 in</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>71</v>
+      </c>
+      <c r="I10" t="n">
+        <v>150</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-10</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Broca HSS 11/32 in</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>150</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-11</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Broca HSS 3/8 in</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>150</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Broca HSS 13/32 in</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>150</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-13</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Broca HSS 7/16 in</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>150</v>
+      </c>
+      <c r="J14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Broca HSS 15/32 in</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>150</v>
+      </c>
+      <c r="J15" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C3-02-15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Broca HSS 1/2 in</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>150</v>
+      </c>
+      <c r="J16" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-01</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Dado 1 in 1/2 12 puntas</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>199</v>
+      </c>
+      <c r="H17" t="n">
+        <v>202</v>
+      </c>
+      <c r="I17" t="n">
+        <v>34</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>106482</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-02</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Dado 15/16 in 1/2 12 puntas</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>201.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>170</v>
+      </c>
+      <c r="I18" t="n">
+        <v>29</v>
+      </c>
+      <c r="J18" t="n">
+        <v>29</v>
+      </c>
+      <c r="K18" t="n">
+        <v>36</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>106483</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-03</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Dado 7/8 in 1/2 12 puntas</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>140</v>
+      </c>
+      <c r="I19" t="n">
+        <v>27</v>
+      </c>
+      <c r="J19" t="n">
+        <v>27</v>
+      </c>
+      <c r="K19" t="n">
+        <v>35</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>106484</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-04</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Dado 13/16 in 1/2 12 puntas</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>112</v>
+      </c>
+      <c r="I20" t="n">
+        <v>25</v>
+      </c>
+      <c r="J20" t="n">
+        <v>25</v>
+      </c>
+      <c r="K20" t="n">
+        <v>35</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>106485</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-05</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Dado 18 mm 3/8</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>204</v>
+      </c>
+      <c r="H21" t="n">
+        <v>85</v>
+      </c>
+      <c r="I21" t="n">
+        <v>24</v>
+      </c>
+      <c r="J21" t="n">
+        <v>24</v>
+      </c>
+      <c r="K21" t="n">
+        <v>26</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>129325</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-06</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Dado 18 mm 3/8</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>204</v>
+      </c>
+      <c r="H22" t="n">
+        <v>58</v>
+      </c>
+      <c r="I22" t="n">
+        <v>24</v>
+      </c>
+      <c r="J22" t="n">
+        <v>24</v>
+      </c>
+      <c r="K22" t="n">
+        <v>26</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>129325</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-07</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Dado 19 mm 3/8</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>204.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>32</v>
+      </c>
+      <c r="I23" t="n">
+        <v>23</v>
+      </c>
+      <c r="J23" t="n">
+        <v>23</v>
+      </c>
+      <c r="K23" t="n">
+        <v>22</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>129326</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-08</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Dado 3/4 in 3/8</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>204.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>23</v>
+      </c>
+      <c r="J24" t="n">
+        <v>23</v>
+      </c>
+      <c r="K24" t="n">
+        <v>23</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>106507</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-09</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Dado 3/4 in 3/8</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>236</v>
+      </c>
+      <c r="H25" t="n">
+        <v>213</v>
+      </c>
+      <c r="I25" t="n">
+        <v>23</v>
+      </c>
+      <c r="J25" t="n">
+        <v>23</v>
+      </c>
+      <c r="K25" t="n">
+        <v>23</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>106507</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-10</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Dado 3/4 in 3/8</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>236</v>
+      </c>
+      <c r="H26" t="n">
+        <v>187</v>
+      </c>
+      <c r="I26" t="n">
+        <v>23</v>
+      </c>
+      <c r="J26" t="n">
+        <v>23</v>
+      </c>
+      <c r="K26" t="n">
+        <v>23</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>106507</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-11</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Dado 11/16 in 3/8</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>236.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>162</v>
+      </c>
+      <c r="I27" t="n">
+        <v>22</v>
+      </c>
+      <c r="J27" t="n">
+        <v>22</v>
+      </c>
+      <c r="K27" t="n">
+        <v>26</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>106509</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-12</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Dado 17 mm 3/8</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>237</v>
+      </c>
+      <c r="H28" t="n">
+        <v>138</v>
+      </c>
+      <c r="I28" t="n">
+        <v>21</v>
+      </c>
+      <c r="J28" t="n">
+        <v>21</v>
+      </c>
+      <c r="K28" t="n">
+        <v>23</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>129323</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-13</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Dado 16 mm 1/2 12 puntas</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>115</v>
+      </c>
+      <c r="I29" t="n">
+        <v>20</v>
+      </c>
+      <c r="J29" t="n">
+        <v>20</v>
+      </c>
+      <c r="K29" t="n">
+        <v>35</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>106503</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-14</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Dado 5/8 in 3/8</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>92</v>
+      </c>
+      <c r="I30" t="n">
+        <v>20</v>
+      </c>
+      <c r="J30" t="n">
+        <v>20</v>
+      </c>
+      <c r="K30" t="n">
+        <v>22</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>106510</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-15</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Dado 11 mm 3/8 (SIN FICHA: se usa el del 10 mm)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>238</v>
+      </c>
+      <c r="H31" t="n">
+        <v>70</v>
+      </c>
+      <c r="I31" t="n">
+        <v>19</v>
+      </c>
+      <c r="J31" t="n">
+        <v>19</v>
+      </c>
+      <c r="K31" t="n">
+        <v>24</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>supuesto (sin ficha)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-16</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Dado 10 mm 3/8</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>238</v>
+      </c>
+      <c r="H32" t="n">
+        <v>48</v>
+      </c>
+      <c r="I32" t="n">
+        <v>19</v>
+      </c>
+      <c r="J32" t="n">
+        <v>19</v>
+      </c>
+      <c r="K32" t="n">
+        <v>24</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>129318</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-17</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Dado 15 mm 3/8</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>27</v>
+      </c>
+      <c r="I33" t="n">
+        <v>18</v>
+      </c>
+      <c r="J33" t="n">
+        <v>18</v>
+      </c>
+      <c r="K33" t="n">
+        <v>21</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>129322</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-18</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Dado 15 mm 3/8</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I34" t="n">
+        <v>18</v>
+      </c>
+      <c r="J34" t="n">
+        <v>18</v>
+      </c>
+      <c r="K34" t="n">
+        <v>21</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>129322</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-19</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Dado 14 mm 3/8</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>262</v>
+      </c>
+      <c r="H35" t="n">
+        <v>219</v>
+      </c>
+      <c r="I35" t="n">
+        <v>17</v>
+      </c>
+      <c r="J35" t="n">
+        <v>17</v>
+      </c>
+      <c r="K35" t="n">
+        <v>22</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>129321</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-20</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Dado 9/16 in 3/8</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>262</v>
+      </c>
+      <c r="H36" t="n">
+        <v>199</v>
+      </c>
+      <c r="I36" t="n">
+        <v>17</v>
+      </c>
+      <c r="J36" t="n">
+        <v>17</v>
+      </c>
+      <c r="K36" t="n">
+        <v>22</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>106511</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-21</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Dado 13 mm 3/8</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>180</v>
+      </c>
+      <c r="I37" t="n">
+        <v>16</v>
+      </c>
+      <c r="J37" t="n">
+        <v>16</v>
+      </c>
+      <c r="K37" t="n">
+        <v>21</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>129320</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-22</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Dado 1/2 in 3/8</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>161</v>
+      </c>
+      <c r="I38" t="n">
+        <v>16</v>
+      </c>
+      <c r="J38" t="n">
+        <v>16</v>
+      </c>
+      <c r="K38" t="n">
+        <v>21</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>106512</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-23</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Dado 1/2 in 3/8</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>142</v>
+      </c>
+      <c r="I39" t="n">
+        <v>16</v>
+      </c>
+      <c r="J39" t="n">
+        <v>16</v>
+      </c>
+      <c r="K39" t="n">
+        <v>21</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>106512</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-24</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Dado 3/8 in 3/8</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>263</v>
+      </c>
+      <c r="H40" t="n">
+        <v>124</v>
+      </c>
+      <c r="I40" t="n">
+        <v>15</v>
+      </c>
+      <c r="J40" t="n">
+        <v>15</v>
+      </c>
+      <c r="K40" t="n">
+        <v>22</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>106514</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-25</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Dado 12 mm 3/8</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>107</v>
+      </c>
+      <c r="I41" t="n">
+        <v>14</v>
+      </c>
+      <c r="J41" t="n">
+        <v>14</v>
+      </c>
+      <c r="K41" t="n">
+        <v>22</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>129319</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-26</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Dado 5/16 in</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>90</v>
+      </c>
+      <c r="I42" t="n">
+        <v>14</v>
+      </c>
+      <c r="J42" t="n">
+        <v>14</v>
+      </c>
+      <c r="K42" t="n">
+        <v>22</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>106513</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-27</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Dado 7/16 in 3/8</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>73</v>
+      </c>
+      <c r="I43" t="n">
+        <v>14</v>
+      </c>
+      <c r="J43" t="n">
+        <v>14</v>
+      </c>
+      <c r="K43" t="n">
+        <v>24</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>106515</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-28</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Dado 7/16 in 3/8</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>56</v>
+      </c>
+      <c r="I44" t="n">
+        <v>14</v>
+      </c>
+      <c r="J44" t="n">
+        <v>14</v>
+      </c>
+      <c r="K44" t="n">
+        <v>24</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>106515</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C4-04-29</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Dado 7/16 in 3/8</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>circulo</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>39</v>
+      </c>
+      <c r="I45" t="n">
+        <v>14</v>
+      </c>
+      <c r="J45" t="n">
+        <v>14</v>
+      </c>
+      <c r="K45" t="n">
+        <v>24</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>106515</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C5-02</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C5-02-01</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Desarmador Husky P1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" t="n">
+        <v>12</v>
+      </c>
+      <c r="I46" t="n">
+        <v>230</v>
+      </c>
+      <c r="J46" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="K46" t="n">
+        <v>32</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>F (envolvente del juego / n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C5-02</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C5-02-02</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Desarmador Husky P1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>6</v>
+      </c>
+      <c r="H47" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="I47" t="n">
+        <v>230</v>
+      </c>
+      <c r="J47" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="K47" t="n">
+        <v>32</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>F (envolvente del juego / n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C5-02</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C5-02-03</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Desarmador Husky P2</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H48" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="I48" t="n">
+        <v>230</v>
+      </c>
+      <c r="J48" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="K48" t="n">
+        <v>32</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>F (envolvente del juego / n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-01</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-01-01</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Desarmador Husky P2</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>6</v>
+      </c>
+      <c r="H49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I49" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J49" t="n">
+        <v>230</v>
+      </c>
+      <c r="K49" t="n">
+        <v>32</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>F (envolvente del juego / n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-01</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-01-02</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Desarmador Husky P2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="H50" t="n">
+        <v>6</v>
+      </c>
+      <c r="I50" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J50" t="n">
+        <v>230</v>
+      </c>
+      <c r="K50" t="n">
+        <v>32</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>F (envolvente del juego / n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-01</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-01-03</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Desarmador Husky P2</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="H51" t="n">
+        <v>6</v>
+      </c>
+      <c r="I51" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>230</v>
+      </c>
+      <c r="K51" t="n">
+        <v>32</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>F (envolvente del juego / n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-03</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-03-01</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Extension 3/8 de 6 in</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>118</v>
+      </c>
+      <c r="H52" t="n">
+        <v>128</v>
+      </c>
+      <c r="I52" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="K52" t="n">
+        <v>25</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-03</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-03-02</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Extension 3/8 de 10 in</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>118</v>
+      </c>
+      <c r="H53" t="n">
+        <v>155.7</v>
+      </c>
+      <c r="I53" t="n">
+        <v>254</v>
+      </c>
+      <c r="J53" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="K53" t="n">
+        <v>25</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-03</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-03-03</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Maneral de fuerza 3/8</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>118</v>
+      </c>
+      <c r="H54" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="I54" t="n">
+        <v>230</v>
+      </c>
+      <c r="J54" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="K54" t="n">
+        <v>25</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-04</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-04-01</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Desarmador de precision 1 de 6</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>118</v>
+      </c>
+      <c r="H55" t="n">
+        <v>220</v>
+      </c>
+      <c r="I55" t="n">
+        <v>190</v>
+      </c>
+      <c r="J55" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K55" t="n">
+        <v>25</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>F (envolvente del juego / n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-04</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-04-02</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Desarmador de precision 2 de 6</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>118</v>
+      </c>
+      <c r="H56" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="I56" t="n">
+        <v>190</v>
+      </c>
+      <c r="J56" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>25</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>F (envolvente del juego / n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-04</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-04-03</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Desarmador de precision 3 de 6</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>118</v>
+      </c>
+      <c r="H57" t="n">
+        <v>251</v>
+      </c>
+      <c r="I57" t="n">
+        <v>190</v>
+      </c>
+      <c r="J57" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K57" t="n">
+        <v>25</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>F (envolvente del juego / n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-04</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-04-04</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Desarmador de precision 4 de 6</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>118</v>
+      </c>
+      <c r="H58" t="n">
+        <v>266.5</v>
+      </c>
+      <c r="I58" t="n">
+        <v>190</v>
+      </c>
+      <c r="J58" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>25</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>F (envolvente del juego / n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-04</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-04-05</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Desarmador de precision 5 de 6</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>118</v>
+      </c>
+      <c r="H59" t="n">
+        <v>282</v>
+      </c>
+      <c r="I59" t="n">
+        <v>190</v>
+      </c>
+      <c r="J59" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K59" t="n">
+        <v>25</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>F (envolvente del juego / n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-04</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-04-06</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Desarmador de precision 6 de 6</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>118</v>
+      </c>
+      <c r="H60" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="I60" t="n">
+        <v>190</v>
+      </c>
+      <c r="J60" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>25</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>F (envolvente del juego / n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-05</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-05-01</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Adaptador 1/4 a 3/8</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>320</v>
+      </c>
+      <c r="H61" t="n">
+        <v>220</v>
+      </c>
+      <c r="I61" t="n">
+        <v>70</v>
+      </c>
+      <c r="J61" t="n">
+        <v>19</v>
+      </c>
+      <c r="K61" t="n">
+        <v>25</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-05</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-05-02</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adaptador 3/8 a 1/2</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>320</v>
+      </c>
+      <c r="H62" t="n">
+        <v>242</v>
+      </c>
+      <c r="I62" t="n">
+        <v>70</v>
+      </c>
+      <c r="J62" t="n">
+        <v>19</v>
+      </c>
+      <c r="K62" t="n">
+        <v>25</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-05</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>FTS-BAS-01-C6-05-03</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Adaptador 1/2 a 3/8</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>barra</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>320</v>
+      </c>
+      <c r="H63" t="n">
+        <v>264</v>
+      </c>
+      <c r="I63" t="n">
+        <v>70</v>
+      </c>
+      <c r="J63" t="n">
+        <v>19</v>
+      </c>
+      <c r="K63" t="n">
+        <v>25</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>ver fuente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14344,7 +17894,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15166,7 +18716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16465,7 +20015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16783,7 +20333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16898,7 +20448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17243,7 +20793,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
